--- a/docs/PRAP_Development_Plan_v1.4.xlsx
+++ b/docs/PRAP_Development_Plan_v1.4.xlsx
@@ -7001,7 +7001,7 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>The set of periods a project carries depends on its type: 'Clinical Trial' uses Before-Start-up / Start-up / Conduct / Close-out (interim) / Close-out (final) / After Close-out (final); 'Others' uses Planning / Develop / Close.</t>
+          <t>The set of periods a project carries depends on its type: either clinical trial type uses Before-Start-up / Start-up / Conduct / Close-out (interim) / Close-out (final) / After Close-out (final); 'Others' uses Planning / Develop / Close.</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>A 'Clinical Trial' project records its clinical phase (phase 1 / 2 / 3 / 4). The phase determines the project's period weights, so it drives the simulation rather than merely describing the project.</t>
+          <t>A clinical trial of either type records its clinical phase (phase 1 / 2 / 3 / 4). The phase determines the project's period weights, so it drives the simulation rather than merely describing the project.</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>A 'Clinical Trial' project records who performs each of EDC set-up, data-review-system set-up, RBQM set-up and DM conduct ('by CRO' / 'by SB').</t>
+          <t>A clinical trial of either type records who performs each of EDC set-up, data-review-system set-up, RBQM set-up and DM conduct ('by CRO' / 'by SB').</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>A 'Clinical Trial' project records the EDC system, data review system and RBQM system in use, from data-driven value lists.</t>
+          <t>A clinical trial of either type records the EDC system, data review system and RBQM system in use, from data-driven value lists.</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>For a 'Clinical Trial' project, period boundaries are computed from milestone dates plus fixed month offsets (sheet 05), so a timeline change re-shapes the periods without re-typing them. For 'Others', periods are entered directly - those projects have no milestone mapping.</t>
+          <t>For a clinical trial of either type, period boundaries are computed from milestone dates plus fixed month offsets (sheet 05), so a timeline change re-shapes the periods without re-typing them. For 'Others', periods are entered directly - those projects have no milestone mapping.</t>
         </is>
       </c>
       <c r="D38" s="18" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Product name. Required when project_type = 'Clinical Trial'.</t>
+          <t>Product name. Required for either clinical trial type.</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>'Phase 1' / 'Phase 2' / 'Phase 3' / 'Phase 4'. Required when project_type = 'Clinical Trial'.</t>
+          <t>'Phase 1' / 'Phase 2' / 'Phase 3' / 'Phase 4'. Required for either clinical trial type.</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>Who sets up the EDC system. 'by CRO' / 'by SB'. Required when project_type = 'Clinical Trial'.</t>
+          <t>Who sets up the EDC system. 'by CRO' / 'by SB'. Required for either clinical trial type.</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -9996,17 +9996,17 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>[CHANGED]NewDrug CT / Biosimilar CT</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>NewDrug CT / Biosimilar CT</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
         <is>
           <t>Before-Start-up, Start-up, Conduct, Close-out (interim), Close-out (final), After Close-out (final)</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>Both trial types share one period set and one derivation. They differ in their WEIGHTS, not their shape.</t>
         </is>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>project_category is present when project_type = 'Clinical Trial'.</t>
+          <t>project_category is present for either clinical trial type.</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
@@ -11996,7 +11996,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Period derivation for a 'Clinical Trial' project   [v1.1]</t>
+          <t>Period derivation for a clinical trial - either type   [v1.1]</t>
         </is>
       </c>
     </row>
